--- a/entry/test/fixtures/form-b-pairs.xlsx
+++ b/entry/test/fixtures/form-b-pairs.xlsx
@@ -118,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -141,11 +141,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -153,6 +170,7 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
